--- a/database.xlsx
+++ b/database.xlsx
@@ -1,140 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ocell\Desktop\KNEURATRAX\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23C79210-5DC5-4E24-8DDB-ED0C5D2CA031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
     <sheet name="Ledger" sheetId="1" r:id="rId1"/>
     <sheet name="Rates" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="34">
-  <si>
-    <t>ID (Auto)</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Category</t>
-  </si>
-  <si>
-    <t>Lifecycle Status</t>
-  </si>
-  <si>
-    <t>Paid By</t>
-  </si>
-  <si>
-    <t>Currency</t>
-  </si>
-  <si>
-    <t>Actual (USD)</t>
-  </si>
-  <si>
-    <t>Split %</t>
-  </si>
-  <si>
-    <t>Notes / Invoice Ref</t>
-  </si>
-  <si>
-    <t>Rate Used</t>
-  </si>
-  <si>
-    <t>2026-02-18</t>
-  </si>
-  <si>
-    <t>Expense</t>
-  </si>
-  <si>
-    <t>Legal Fees for the Company Formation</t>
-  </si>
-  <si>
-    <t>Legal</t>
-  </si>
-  <si>
-    <t>Paid</t>
-  </si>
-  <si>
-    <t>Gautham</t>
-  </si>
-  <si>
-    <t>USD</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>2026-02-19</t>
-  </si>
-  <si>
-    <t>Bought Web Domain from Godaddy</t>
-  </si>
-  <si>
-    <t>Infrastructure</t>
-  </si>
-  <si>
-    <t>Piyal</t>
-  </si>
-  <si>
-    <t>2026-02-28</t>
-  </si>
-  <si>
-    <t>Bought Email Domain from Godaddy</t>
-  </si>
-  <si>
-    <t>2026-04-06</t>
-  </si>
-  <si>
-    <t>Income</t>
-  </si>
-  <si>
-    <t>Terraintel360</t>
-  </si>
-  <si>
-    <t>Payment received</t>
-  </si>
-  <si>
-    <t>Budgeted</t>
-  </si>
-  <si>
-    <t>Tracy M Griggs</t>
-  </si>
-  <si>
-    <t>Live Rate</t>
-  </si>
-  <si>
-    <t>Fallback</t>
-  </si>
-</sst>
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
+  <fonts count="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -171,14 +73,6 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -503,86 +397,71 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="8.08203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.9140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="32.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.08203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.25" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L4"/>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>ID (Auto)</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Date</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Type</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Description</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Category</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Lifecycle Status</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Paid By</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Currency</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Actual (USD)</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Split %</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Notes / Invoice Ref</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Rate Used</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="2">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" t="s">
-        <v>18</v>
+      <c r="B2" t="str">
+        <v>2026-02-18</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Legal Fees for the Company Formation</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Miscellaneous</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Gautham</v>
+      </c>
+      <c r="H2" t="str">
+        <v>USD</v>
       </c>
       <c r="I2">
         <v>120</v>
@@ -590,37 +469,37 @@
       <c r="J2">
         <v>50</v>
       </c>
-      <c r="K2" t="s">
-        <v>19</v>
+      <c r="K2" t="str">
+        <v/>
       </c>
       <c r="L2">
         <v>84</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="3">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3" t="s">
-        <v>18</v>
+      <c r="B3" t="str">
+        <v>2026-02-19</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Bought Web Domain from Godaddy</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Miscellaneous</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Piyal</v>
+      </c>
+      <c r="H3" t="str">
+        <v>USD</v>
       </c>
       <c r="I3">
         <v>22.7</v>
@@ -628,37 +507,37 @@
       <c r="J3">
         <v>50</v>
       </c>
-      <c r="K3" t="s">
-        <v>19</v>
+      <c r="K3" t="str">
+        <v/>
       </c>
       <c r="L3">
         <v>84</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="4">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4" t="s">
-        <v>18</v>
+      <c r="B4" t="str">
+        <v>2026-02-28</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Bought Email Domain from Godaddy</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Miscellaneous</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Piyal</v>
+      </c>
+      <c r="H4" t="str">
+        <v>USD</v>
       </c>
       <c r="I4">
         <v>19.71</v>
@@ -666,84 +545,43 @@
       <c r="J4">
         <v>50</v>
       </c>
-      <c r="K4" t="s">
-        <v>19</v>
+      <c r="K4" t="str">
+        <v/>
       </c>
       <c r="L4">
         <v>84</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G5" t="s">
-        <v>31</v>
-      </c>
-      <c r="H5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I5">
-        <v>8000</v>
-      </c>
-      <c r="J5">
-        <v>50</v>
-      </c>
-      <c r="K5" t="s">
-        <v>19</v>
-      </c>
-      <c r="L5">
-        <v>95</v>
-      </c>
-    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:L4 A5:K5" numberStoredAsText="1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>32</v>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Live Rate</v>
       </c>
       <c r="B1">
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>33</v>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Fallback</v>
       </c>
       <c r="B2">
         <v>84</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:B2" numberStoredAsText="1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/database.xlsx
+++ b/database.xlsx
@@ -452,7 +452,7 @@
         <v>Legal Fees for the Company Formation</v>
       </c>
       <c r="E2" t="str">
-        <v>Miscellaneous</v>
+        <v>Legal &amp; Compliance</v>
       </c>
       <c r="F2" t="str">
         <v>Paid</v>
@@ -490,7 +490,7 @@
         <v>Bought Web Domain from Godaddy</v>
       </c>
       <c r="E3" t="str">
-        <v>Miscellaneous</v>
+        <v>Subscriptions (SaaS, research, cloud)</v>
       </c>
       <c r="F3" t="str">
         <v>Paid</v>
@@ -528,7 +528,7 @@
         <v>Bought Email Domain from Godaddy</v>
       </c>
       <c r="E4" t="str">
-        <v>Miscellaneous</v>
+        <v>Subscriptions (SaaS, research, cloud)</v>
       </c>
       <c r="F4" t="str">
         <v>Paid</v>

--- a/database.xlsx
+++ b/database.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -443,7 +443,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="C2" t="str">
         <v>Expense</v>
@@ -481,7 +481,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="C3" t="str">
         <v>Expense</v>
@@ -519,7 +519,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-02-28</v>
+        <v>2026-03-01</v>
       </c>
       <c r="C4" t="str">
         <v>Expense</v>
@@ -549,12 +549,50 @@
         <v/>
       </c>
       <c r="L4">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Income</v>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+      <c r="E5" t="str">
+        <v>Accounting / Finance</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Budgeted</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Tracy M Griggs</v>
+      </c>
+      <c r="H5" t="str">
+        <v>USD</v>
+      </c>
+      <c r="I5">
+        <v>8000</v>
+      </c>
+      <c r="J5">
+        <v>50</v>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5">
         <v>84</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/database.xlsx
+++ b/database.xlsx
@@ -563,7 +563,7 @@
         <v>Income</v>
       </c>
       <c r="D5" t="str">
-        <v/>
+        <v>Terraintel360</v>
       </c>
       <c r="E5" t="str">
         <v>Accounting / Finance</v>

--- a/database.xlsx
+++ b/database.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -590,9 +590,47 @@
         <v>84</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-05-14</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Income</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Business Travel to US - Piyal - 2026</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Miscellaneous</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Budgeted</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Piyal</v>
+      </c>
+      <c r="H6" t="str">
+        <v>USD</v>
+      </c>
+      <c r="I6">
+        <v>2000</v>
+      </c>
+      <c r="J6">
+        <v>50</v>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6">
+        <v>93</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/database.xlsx
+++ b/database.xlsx
@@ -598,13 +598,13 @@
         <v>2026-05-14</v>
       </c>
       <c r="C6" t="str">
-        <v>Income</v>
+        <v>Expense</v>
       </c>
       <c r="D6" t="str">
         <v>Business Travel to US - Piyal - 2026</v>
       </c>
       <c r="E6" t="str">
-        <v>Miscellaneous</v>
+        <v>Travel &amp; Client Meetings</v>
       </c>
       <c r="F6" t="str">
         <v>Budgeted</v>

--- a/database.xlsx
+++ b/database.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -557,28 +557,28 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-06-01</v>
+        <v>2026-05-14</v>
       </c>
       <c r="C5" t="str">
-        <v>Income</v>
+        <v>Expense</v>
       </c>
       <c r="D5" t="str">
-        <v>Terraintel360</v>
+        <v>Business Travel to US - Piyal - 2026</v>
       </c>
       <c r="E5" t="str">
-        <v>Accounting / Finance</v>
+        <v>Travel &amp; Client Meetings</v>
       </c>
       <c r="F5" t="str">
         <v>Budgeted</v>
       </c>
       <c r="G5" t="str">
-        <v>Tracy M Griggs</v>
+        <v>Piyal</v>
       </c>
       <c r="H5" t="str">
         <v>USD</v>
       </c>
       <c r="I5">
-        <v>8000</v>
+        <v>2000</v>
       </c>
       <c r="J5">
         <v>50</v>
@@ -587,50 +587,12 @@
         <v/>
       </c>
       <c r="L5">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-05-14</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Expense</v>
-      </c>
-      <c r="D6" t="str">
-        <v>Business Travel to US - Piyal - 2026</v>
-      </c>
-      <c r="E6" t="str">
-        <v>Travel &amp; Client Meetings</v>
-      </c>
-      <c r="F6" t="str">
-        <v>Budgeted</v>
-      </c>
-      <c r="G6" t="str">
-        <v>Piyal</v>
-      </c>
-      <c r="H6" t="str">
-        <v>USD</v>
-      </c>
-      <c r="I6">
-        <v>2000</v>
-      </c>
-      <c r="J6">
-        <v>50</v>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6">
         <v>93</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/database.xlsx
+++ b/database.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -552,47 +552,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-05-14</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Expense</v>
-      </c>
-      <c r="D5" t="str">
-        <v>Business Travel to US - Piyal - 2026</v>
-      </c>
-      <c r="E5" t="str">
-        <v>Travel &amp; Client Meetings</v>
-      </c>
-      <c r="F5" t="str">
-        <v>Budgeted</v>
-      </c>
-      <c r="G5" t="str">
-        <v>Piyal</v>
-      </c>
-      <c r="H5" t="str">
-        <v>USD</v>
-      </c>
-      <c r="I5">
-        <v>2000</v>
-      </c>
-      <c r="J5">
-        <v>50</v>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5">
-        <v>93</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/database.xlsx
+++ b/database.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -552,9 +552,47 @@
         <v>84</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-05-14</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+      <c r="E5" t="str">
+        <v>Miscellaneous</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Budgeted</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Piyal</v>
+      </c>
+      <c r="H5" t="str">
+        <v>USD</v>
+      </c>
+      <c r="I5">
+        <v>2000</v>
+      </c>
+      <c r="J5">
+        <v>50</v>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5">
+        <v>93.13</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -568,7 +606,7 @@
         <v>Live Rate</v>
       </c>
       <c r="B1">
-        <v>84</v>
+        <v>93.125844</v>
       </c>
     </row>
     <row r="2">

--- a/database.xlsx
+++ b/database.xlsx
@@ -563,10 +563,10 @@
         <v>Expense</v>
       </c>
       <c r="D5" t="str">
-        <v/>
+        <v>Business Travel to US - Piyal - 2026</v>
       </c>
       <c r="E5" t="str">
-        <v>Miscellaneous</v>
+        <v>Travel &amp; Client Meetings</v>
       </c>
       <c r="F5" t="str">
         <v>Budgeted</v>

--- a/database.xlsx
+++ b/database.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -590,9 +590,47 @@
         <v>93.13</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-04-08</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="D6" t="str">
+        <v xml:space="preserve">Claude Pro Version </v>
+      </c>
+      <c r="E6" t="str">
+        <v>Subscriptions (SaaS, research, cloud)</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Gautham</v>
+      </c>
+      <c r="H6" t="str">
+        <v>USD</v>
+      </c>
+      <c r="I6">
+        <v>20</v>
+      </c>
+      <c r="J6">
+        <v>50</v>
+      </c>
+      <c r="K6" t="str">
+        <v>MV9KTJMD-0001</v>
+      </c>
+      <c r="L6">
+        <v>93.125844</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/database.xlsx
+++ b/database.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -557,80 +557,42 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-05-14</v>
+        <v>2026-04-08</v>
       </c>
       <c r="C5" t="str">
         <v>Expense</v>
       </c>
       <c r="D5" t="str">
-        <v>Business Travel to US - Piyal - 2026</v>
+        <v>Claude Pro Version</v>
       </c>
       <c r="E5" t="str">
-        <v>Travel &amp; Client Meetings</v>
+        <v>Subscriptions (SaaS, research, cloud)</v>
       </c>
       <c r="F5" t="str">
-        <v>Budgeted</v>
+        <v>Paid</v>
       </c>
       <c r="G5" t="str">
-        <v>Piyal</v>
+        <v>Gautham</v>
       </c>
       <c r="H5" t="str">
         <v>USD</v>
       </c>
       <c r="I5">
-        <v>2000</v>
+        <v>20</v>
       </c>
       <c r="J5">
         <v>50</v>
       </c>
       <c r="K5" t="str">
-        <v/>
+        <v>MV9KTJMD-0001</v>
       </c>
       <c r="L5">
-        <v>93.13</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-04-08</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Expense</v>
-      </c>
-      <c r="D6" t="str">
-        <v xml:space="preserve">Claude Pro Version </v>
-      </c>
-      <c r="E6" t="str">
-        <v>Subscriptions (SaaS, research, cloud)</v>
-      </c>
-      <c r="F6" t="str">
-        <v>Paid</v>
-      </c>
-      <c r="G6" t="str">
-        <v>Gautham</v>
-      </c>
-      <c r="H6" t="str">
-        <v>USD</v>
-      </c>
-      <c r="I6">
-        <v>20</v>
-      </c>
-      <c r="J6">
-        <v>50</v>
-      </c>
-      <c r="K6" t="str">
-        <v>MV9KTJMD-0001</v>
-      </c>
-      <c r="L6">
         <v>93.125844</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/database.xlsx
+++ b/database.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -590,9 +590,47 @@
         <v>93.125844</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Income</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Travel to US</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Miscellaneous</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Budgeted</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Piyal</v>
+      </c>
+      <c r="H6" t="str">
+        <v>USD</v>
+      </c>
+      <c r="I6">
+        <v>1000</v>
+      </c>
+      <c r="J6">
+        <v>50</v>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6">
+        <v>93.125844</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/database.xlsx
+++ b/database.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -590,47 +590,9 @@
         <v>93.125844</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-05-01</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Income</v>
-      </c>
-      <c r="D6" t="str">
-        <v>Travel to US</v>
-      </c>
-      <c r="E6" t="str">
-        <v>Miscellaneous</v>
-      </c>
-      <c r="F6" t="str">
-        <v>Budgeted</v>
-      </c>
-      <c r="G6" t="str">
-        <v>Piyal</v>
-      </c>
-      <c r="H6" t="str">
-        <v>USD</v>
-      </c>
-      <c r="I6">
-        <v>1000</v>
-      </c>
-      <c r="J6">
-        <v>50</v>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6">
-        <v>93.125844</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/database.xlsx
+++ b/database.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -590,9 +590,47 @@
         <v>93.125844</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Travel to US</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Travel &amp; Client Meetings</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Budgeted</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Piyal</v>
+      </c>
+      <c r="H6" t="str">
+        <v>USD</v>
+      </c>
+      <c r="I6">
+        <v>1000</v>
+      </c>
+      <c r="J6">
+        <v>50</v>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6">
+        <v>93.125844</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/database.xlsx
+++ b/database.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -590,47 +590,9 @@
         <v>93.125844</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-05-01</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Expense</v>
-      </c>
-      <c r="D6" t="str">
-        <v>Travel to US</v>
-      </c>
-      <c r="E6" t="str">
-        <v>Travel &amp; Client Meetings</v>
-      </c>
-      <c r="F6" t="str">
-        <v>Budgeted</v>
-      </c>
-      <c r="G6" t="str">
-        <v>Piyal</v>
-      </c>
-      <c r="H6" t="str">
-        <v>USD</v>
-      </c>
-      <c r="I6">
-        <v>1000</v>
-      </c>
-      <c r="J6">
-        <v>50</v>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6">
-        <v>93.125844</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/database.xlsx
+++ b/database.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -590,9 +590,47 @@
         <v>93.125844</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Income</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Travel to US</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Travel &amp; Client Meetings</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Budgeted</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Piyal</v>
+      </c>
+      <c r="H6" t="str">
+        <v>USD</v>
+      </c>
+      <c r="I6">
+        <v>1000</v>
+      </c>
+      <c r="J6">
+        <v>50</v>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6">
+        <v>93.125844</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/database.xlsx
+++ b/database.xlsx
@@ -601,22 +601,22 @@
         <v>Income</v>
       </c>
       <c r="D6" t="str">
-        <v>Travel to US</v>
+        <v/>
       </c>
       <c r="E6" t="str">
-        <v>Travel &amp; Client Meetings</v>
+        <v>Miscellaneous</v>
       </c>
       <c r="F6" t="str">
         <v>Budgeted</v>
       </c>
       <c r="G6" t="str">
-        <v>Piyal</v>
+        <v/>
       </c>
       <c r="H6" t="str">
         <v>USD</v>
       </c>
       <c r="I6">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J6">
         <v>50</v>

--- a/database.xlsx
+++ b/database.xlsx
@@ -601,7 +601,7 @@
         <v>Income</v>
       </c>
       <c r="D6" t="str">
-        <v/>
+        <v>Travel to Connecticut</v>
       </c>
       <c r="E6" t="str">
         <v>Miscellaneous</v>
@@ -610,13 +610,13 @@
         <v>Budgeted</v>
       </c>
       <c r="G6" t="str">
-        <v/>
+        <v>Piyal</v>
       </c>
       <c r="H6" t="str">
         <v>USD</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J6">
         <v>50</v>

--- a/database.xlsx
+++ b/database.xlsx
@@ -598,7 +598,7 @@
         <v>2026-05-01</v>
       </c>
       <c r="C6" t="str">
-        <v>Income</v>
+        <v>Expense</v>
       </c>
       <c r="D6" t="str">
         <v>Travel to Connecticut</v>

--- a/database.xlsx
+++ b/database.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -590,47 +590,9 @@
         <v>93.125844</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-05-01</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Expense</v>
-      </c>
-      <c r="D6" t="str">
-        <v>Travel to Connecticut</v>
-      </c>
-      <c r="E6" t="str">
-        <v>Miscellaneous</v>
-      </c>
-      <c r="F6" t="str">
-        <v>Budgeted</v>
-      </c>
-      <c r="G6" t="str">
-        <v>Piyal</v>
-      </c>
-      <c r="H6" t="str">
-        <v>USD</v>
-      </c>
-      <c r="I6">
-        <v>1000</v>
-      </c>
-      <c r="J6">
-        <v>50</v>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6">
-        <v>93.125844</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
   </ignoredErrors>
 </worksheet>
 </file>
